--- a/ai-training-prompt-engineering/references/Prompt_Template_Configurator.xlsx
+++ b/ai-training-prompt-engineering/references/Prompt_Template_Configurator.xlsx
@@ -243,7 +243,7 @@
     <t xml:space="preserve">Display return rates to three decimal places while retaining calculation precision.</t>
   </si>
   <si>
-    <t xml:space="preserve">Check displayed 0.349% against the underlying ratio.</t>
+    <t xml:space="preserve">Check displayed 0.348% against the underlying ratio.</t>
   </si>
   <si>
     <t xml:space="preserve">Formula traceability</t>
@@ -5042,7 +5042,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -5051,6 +5051,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="90"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="6" min="6" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="7" min="7" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5111,7 +5112,11 @@
         <v>28</v>
       </c>
       <c r="F7" s="0" t="str">
-        <f aca="false">IF($A7="Yes","- "&amp;$C7,"")</f>
+        <f aca="false">IF(AND($A7="Yes",$C7&lt;&gt;""),"- "&amp;$C7,"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="0" t="str">
+        <f aca="false">IF($A7="Yes","- "&amp;$D7,"")</f>
         <v/>
       </c>
     </row>
@@ -5129,7 +5134,11 @@
         <v>31</v>
       </c>
       <c r="F8" s="0" t="str">
-        <f aca="false">IF($A8="Yes","- "&amp;$C8,"")</f>
+        <f aca="false">IF(AND($A8="Yes",$C8&lt;&gt;""),"- "&amp;$C8,"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="0" t="str">
+        <f aca="false">IF($A8="Yes","- "&amp;$D8,"")</f>
         <v/>
       </c>
     </row>
@@ -5147,7 +5156,11 @@
         <v>34</v>
       </c>
       <c r="F9" s="0" t="str">
-        <f aca="false">IF($A9="Yes","- "&amp;$C9,"")</f>
+        <f aca="false">IF(AND($A9="Yes",$C9&lt;&gt;""),"- "&amp;$C9,"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="0" t="str">
+        <f aca="false">IF($A9="Yes","- "&amp;$D9,"")</f>
         <v/>
       </c>
     </row>
@@ -5165,7 +5178,11 @@
         <v>37</v>
       </c>
       <c r="F10" s="0" t="str">
-        <f aca="false">IF($A10="Yes","- "&amp;$C10,"")</f>
+        <f aca="false">IF(AND($A10="Yes",$C10&lt;&gt;""),"- "&amp;$C10,"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="0" t="str">
+        <f aca="false">IF($A10="Yes","- "&amp;$D10,"")</f>
         <v/>
       </c>
     </row>
@@ -5183,7 +5200,11 @@
         <v>40</v>
       </c>
       <c r="F11" s="0" t="str">
-        <f aca="false">IF($A11="Yes","- "&amp;$C11,"")</f>
+        <f aca="false">IF(AND($A11="Yes",$C11&lt;&gt;""),"- "&amp;$C11,"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="0" t="str">
+        <f aca="false">IF($A11="Yes","- "&amp;$D11,"")</f>
         <v/>
       </c>
     </row>
@@ -5201,7 +5222,11 @@
         <v>43</v>
       </c>
       <c r="F12" s="0" t="str">
-        <f aca="false">IF($A12="Yes","- "&amp;$C12,"")</f>
+        <f aca="false">IF(AND($A12="Yes",$C12&lt;&gt;""),"- "&amp;$C12,"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="0" t="str">
+        <f aca="false">IF($A12="Yes","- "&amp;$D12,"")</f>
         <v/>
       </c>
     </row>
@@ -5219,7 +5244,11 @@
         <v>46</v>
       </c>
       <c r="F13" s="0" t="str">
-        <f aca="false">IF($A13="Yes","- "&amp;$C13,"")</f>
+        <f aca="false">IF(AND($A13="Yes",$C13&lt;&gt;""),"- "&amp;$C13,"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="0" t="str">
+        <f aca="false">IF($A13="Yes","- "&amp;$D13,"")</f>
         <v/>
       </c>
     </row>
@@ -5237,7 +5266,11 @@
         <v>49</v>
       </c>
       <c r="F14" s="0" t="str">
-        <f aca="false">IF($A14="Yes","- "&amp;$C14,"")</f>
+        <f aca="false">IF(AND($A14="Yes",$C14&lt;&gt;""),"- "&amp;$C14,"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="0" t="str">
+        <f aca="false">IF($A14="Yes","- "&amp;$D14,"")</f>
         <v/>
       </c>
     </row>
@@ -5255,7 +5288,11 @@
         <v>52</v>
       </c>
       <c r="F15" s="0" t="str">
-        <f aca="false">IF($A15="Yes","- "&amp;$C15,"")</f>
+        <f aca="false">IF(AND($A15="Yes",$C15&lt;&gt;""),"- "&amp;$C15,"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="0" t="str">
+        <f aca="false">IF($A15="Yes","- "&amp;$D15,"")</f>
         <v/>
       </c>
     </row>
@@ -5273,7 +5310,11 @@
         <v>55</v>
       </c>
       <c r="F16" s="0" t="str">
-        <f aca="false">IF($A16="Yes","- "&amp;$C16,"")</f>
+        <f aca="false">IF(AND($A16="Yes",$C16&lt;&gt;""),"- "&amp;$C16,"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="0" t="str">
+        <f aca="false">IF($A16="Yes","- "&amp;$D16,"")</f>
         <v/>
       </c>
     </row>
@@ -5291,7 +5332,11 @@
         <v>58</v>
       </c>
       <c r="F17" s="0" t="str">
-        <f aca="false">IF($A17="Yes","- "&amp;$C17,"")</f>
+        <f aca="false">IF(AND($A17="Yes",$C17&lt;&gt;""),"- "&amp;$C17,"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="0" t="str">
+        <f aca="false">IF($A17="Yes","- "&amp;$D17,"")</f>
         <v/>
       </c>
     </row>
@@ -5309,7 +5354,11 @@
         <v>61</v>
       </c>
       <c r="F18" s="0" t="str">
-        <f aca="false">IF($A18="Yes","- "&amp;$C18,"")</f>
+        <f aca="false">IF(AND($A18="Yes",$C18&lt;&gt;""),"- "&amp;$C18,"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="0" t="str">
+        <f aca="false">IF($A18="Yes","- "&amp;$D18,"")</f>
         <v/>
       </c>
     </row>
@@ -5327,7 +5376,11 @@
         <v>64</v>
       </c>
       <c r="F19" s="0" t="str">
-        <f aca="false">IF($A19="Yes","- "&amp;$C19,"")</f>
+        <f aca="false">IF(AND($A19="Yes",$C19&lt;&gt;""),"- "&amp;$C19,"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="0" t="str">
+        <f aca="false">IF($A19="Yes","- "&amp;$D19,"")</f>
         <v/>
       </c>
     </row>
@@ -5337,12 +5390,12 @@
       </c>
       <c r="C20" s="13"/>
     </row>
-    <row r="21" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="14" t="s">
         <v>66</v>
       </c>
       <c r="E21" s="8" t="str">
-        <f aca="false">C5&amp;IF(COUNTIF(A7:A19,"Yes")&gt;0,CHAR(10)&amp;CHAR(10)&amp;"Requirements:"&amp;CHAR(10)&amp;_xlfn.TEXTJOIN(CHAR(10),TRUE(),F7:F19),"")&amp;IF(C20&lt;&gt;"",CHAR(10)&amp;CHAR(10)&amp;"Also:"&amp;CHAR(10)&amp;C20,"")</f>
+        <f aca="false">_xlfn.TEXTJOIN(CHAR(10)&amp;CHAR(10),TRUE(),C5,IF(_xlfn.TEXTJOIN(CHAR(10),TRUE(),F7:F19)="","","Requirements:"&amp;CHAR(10)&amp;_xlfn.TEXTJOIN(CHAR(10),TRUE(),F7:F19)),IF(C20="","","Also:"&amp;CHAR(10)&amp;C20),IF(_xlfn.TEXTJOIN(CHAR(10),TRUE(),G7:G19)="","","How I will check the result:"&amp;CHAR(10)&amp;_xlfn.TEXTJOIN(CHAR(10),TRUE(),G7:G19)))</f>
         <v>Help [reader] decide [decision] using [file / sheet], period [range], detail rows only.</v>
       </c>
     </row>
@@ -5399,7 +5452,11 @@
         <v>72</v>
       </c>
       <c r="F27" s="0" t="str">
-        <f aca="false">IF($A27="Yes","- "&amp;$C27,"")</f>
+        <f aca="false">IF(AND($A27="Yes",$C27&lt;&gt;""),"- "&amp;$C27,"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="0" t="str">
+        <f aca="false">IF($A27="Yes","- "&amp;$D27,"")</f>
         <v/>
       </c>
     </row>
@@ -5417,7 +5474,11 @@
         <v>75</v>
       </c>
       <c r="F28" s="0" t="str">
-        <f aca="false">IF($A28="Yes","- "&amp;$C28,"")</f>
+        <f aca="false">IF(AND($A28="Yes",$C28&lt;&gt;""),"- "&amp;$C28,"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="0" t="str">
+        <f aca="false">IF($A28="Yes","- "&amp;$D28,"")</f>
         <v/>
       </c>
     </row>
@@ -5435,7 +5496,11 @@
         <v>78</v>
       </c>
       <c r="F29" s="0" t="str">
-        <f aca="false">IF($A29="Yes","- "&amp;$C29,"")</f>
+        <f aca="false">IF(AND($A29="Yes",$C29&lt;&gt;""),"- "&amp;$C29,"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="0" t="str">
+        <f aca="false">IF($A29="Yes","- "&amp;$D29,"")</f>
         <v/>
       </c>
     </row>
@@ -5453,7 +5518,11 @@
         <v>81</v>
       </c>
       <c r="F30" s="0" t="str">
-        <f aca="false">IF($A30="Yes","- "&amp;$C30,"")</f>
+        <f aca="false">IF(AND($A30="Yes",$C30&lt;&gt;""),"- "&amp;$C30,"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="0" t="str">
+        <f aca="false">IF($A30="Yes","- "&amp;$D30,"")</f>
         <v/>
       </c>
     </row>
@@ -5471,7 +5540,11 @@
         <v>84</v>
       </c>
       <c r="F31" s="0" t="str">
-        <f aca="false">IF($A31="Yes","- "&amp;$C31,"")</f>
+        <f aca="false">IF(AND($A31="Yes",$C31&lt;&gt;""),"- "&amp;$C31,"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="0" t="str">
+        <f aca="false">IF($A31="Yes","- "&amp;$D31,"")</f>
         <v/>
       </c>
     </row>
@@ -5489,7 +5562,11 @@
         <v>87</v>
       </c>
       <c r="F32" s="0" t="str">
-        <f aca="false">IF($A32="Yes","- "&amp;$C32,"")</f>
+        <f aca="false">IF(AND($A32="Yes",$C32&lt;&gt;""),"- "&amp;$C32,"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="0" t="str">
+        <f aca="false">IF($A32="Yes","- "&amp;$D32,"")</f>
         <v/>
       </c>
     </row>
@@ -5507,7 +5584,11 @@
         <v>90</v>
       </c>
       <c r="F33" s="0" t="str">
-        <f aca="false">IF($A33="Yes","- "&amp;$C33,"")</f>
+        <f aca="false">IF(AND($A33="Yes",$C33&lt;&gt;""),"- "&amp;$C33,"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="0" t="str">
+        <f aca="false">IF($A33="Yes","- "&amp;$D33,"")</f>
         <v/>
       </c>
     </row>
@@ -5525,7 +5606,11 @@
         <v>93</v>
       </c>
       <c r="F34" s="0" t="str">
-        <f aca="false">IF($A34="Yes","- "&amp;$C34,"")</f>
+        <f aca="false">IF(AND($A34="Yes",$C34&lt;&gt;""),"- "&amp;$C34,"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="0" t="str">
+        <f aca="false">IF($A34="Yes","- "&amp;$D34,"")</f>
         <v/>
       </c>
     </row>
@@ -5543,7 +5628,11 @@
         <v>96</v>
       </c>
       <c r="F35" s="0" t="str">
-        <f aca="false">IF($A35="Yes","- "&amp;$C35,"")</f>
+        <f aca="false">IF(AND($A35="Yes",$C35&lt;&gt;""),"- "&amp;$C35,"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="0" t="str">
+        <f aca="false">IF($A35="Yes","- "&amp;$D35,"")</f>
         <v/>
       </c>
     </row>
@@ -5561,7 +5650,11 @@
         <v>99</v>
       </c>
       <c r="F36" s="0" t="str">
-        <f aca="false">IF($A36="Yes","- "&amp;$C36,"")</f>
+        <f aca="false">IF(AND($A36="Yes",$C36&lt;&gt;""),"- "&amp;$C36,"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="0" t="str">
+        <f aca="false">IF($A36="Yes","- "&amp;$D36,"")</f>
         <v/>
       </c>
     </row>
@@ -5579,7 +5672,11 @@
         <v>102</v>
       </c>
       <c r="F37" s="0" t="str">
-        <f aca="false">IF($A37="Yes","- "&amp;$C37,"")</f>
+        <f aca="false">IF(AND($A37="Yes",$C37&lt;&gt;""),"- "&amp;$C37,"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="0" t="str">
+        <f aca="false">IF($A37="Yes","- "&amp;$D37,"")</f>
         <v/>
       </c>
     </row>
@@ -5597,7 +5694,11 @@
         <v>105</v>
       </c>
       <c r="F38" s="0" t="str">
-        <f aca="false">IF($A38="Yes","- "&amp;$C38,"")</f>
+        <f aca="false">IF(AND($A38="Yes",$C38&lt;&gt;""),"- "&amp;$C38,"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="0" t="str">
+        <f aca="false">IF($A38="Yes","- "&amp;$D38,"")</f>
         <v/>
       </c>
     </row>
@@ -5615,7 +5716,11 @@
         <v>108</v>
       </c>
       <c r="F39" s="0" t="str">
-        <f aca="false">IF($A39="Yes","- "&amp;$C39,"")</f>
+        <f aca="false">IF(AND($A39="Yes",$C39&lt;&gt;""),"- "&amp;$C39,"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="0" t="str">
+        <f aca="false">IF($A39="Yes","- "&amp;$D39,"")</f>
         <v/>
       </c>
     </row>
@@ -5633,7 +5738,11 @@
         <v>111</v>
       </c>
       <c r="F40" s="0" t="str">
-        <f aca="false">IF($A40="Yes","- "&amp;$C40,"")</f>
+        <f aca="false">IF(AND($A40="Yes",$C40&lt;&gt;""),"- "&amp;$C40,"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="0" t="str">
+        <f aca="false">IF($A40="Yes","- "&amp;$D40,"")</f>
         <v/>
       </c>
     </row>
@@ -5643,12 +5752,12 @@
       </c>
       <c r="C41" s="13"/>
     </row>
-    <row r="42" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="14" t="s">
         <v>66</v>
       </c>
       <c r="E42" s="8" t="str">
-        <f aca="false">C25&amp;IF(COUNTIF(A27:A40,"Yes")&gt;0,CHAR(10)&amp;CHAR(10)&amp;"Requirements:"&amp;CHAR(10)&amp;_xlfn.TEXTJOIN(CHAR(10),TRUE(),F27:F40),"")&amp;IF(C41&lt;&gt;"",CHAR(10)&amp;CHAR(10)&amp;"Also:"&amp;CHAR(10)&amp;C41,"")</f>
+        <f aca="false">_xlfn.TEXTJOIN(CHAR(10)&amp;CHAR(10),TRUE(),C25,IF(_xlfn.TEXTJOIN(CHAR(10),TRUE(),F27:F40)="","","Requirements:"&amp;CHAR(10)&amp;_xlfn.TEXTJOIN(CHAR(10),TRUE(),F27:F40)),IF(C41="","","Also:"&amp;CHAR(10)&amp;C41),IF(_xlfn.TEXTJOIN(CHAR(10),TRUE(),G27:G40)="","","How I will check the result:"&amp;CHAR(10)&amp;_xlfn.TEXTJOIN(CHAR(10),TRUE(),G27:G40)))</f>
         <v>A self-contained offline dashboard for [audience] to explore [data] and answer [question].</v>
       </c>
     </row>
@@ -5705,7 +5814,11 @@
         <v>117</v>
       </c>
       <c r="F48" s="0" t="str">
-        <f aca="false">IF($A48="Yes","- "&amp;$C48,"")</f>
+        <f aca="false">IF(AND($A48="Yes",$C48&lt;&gt;""),"- "&amp;$C48,"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="0" t="str">
+        <f aca="false">IF($A48="Yes","- "&amp;$D48,"")</f>
         <v/>
       </c>
     </row>
@@ -5723,7 +5836,11 @@
         <v>120</v>
       </c>
       <c r="F49" s="0" t="str">
-        <f aca="false">IF($A49="Yes","- "&amp;$C49,"")</f>
+        <f aca="false">IF(AND($A49="Yes",$C49&lt;&gt;""),"- "&amp;$C49,"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="0" t="str">
+        <f aca="false">IF($A49="Yes","- "&amp;$D49,"")</f>
         <v/>
       </c>
     </row>
@@ -5741,7 +5858,11 @@
         <v>123</v>
       </c>
       <c r="F50" s="0" t="str">
-        <f aca="false">IF($A50="Yes","- "&amp;$C50,"")</f>
+        <f aca="false">IF(AND($A50="Yes",$C50&lt;&gt;""),"- "&amp;$C50,"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="0" t="str">
+        <f aca="false">IF($A50="Yes","- "&amp;$D50,"")</f>
         <v/>
       </c>
     </row>
@@ -5759,7 +5880,11 @@
         <v>126</v>
       </c>
       <c r="F51" s="0" t="str">
-        <f aca="false">IF($A51="Yes","- "&amp;$C51,"")</f>
+        <f aca="false">IF(AND($A51="Yes",$C51&lt;&gt;""),"- "&amp;$C51,"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="0" t="str">
+        <f aca="false">IF($A51="Yes","- "&amp;$D51,"")</f>
         <v/>
       </c>
     </row>
@@ -5777,7 +5902,11 @@
         <v>129</v>
       </c>
       <c r="F52" s="0" t="str">
-        <f aca="false">IF($A52="Yes","- "&amp;$C52,"")</f>
+        <f aca="false">IF(AND($A52="Yes",$C52&lt;&gt;""),"- "&amp;$C52,"")</f>
+        <v/>
+      </c>
+      <c r="G52" s="0" t="str">
+        <f aca="false">IF($A52="Yes","- "&amp;$D52,"")</f>
         <v/>
       </c>
     </row>
@@ -5795,7 +5924,11 @@
         <v>132</v>
       </c>
       <c r="F53" s="0" t="str">
-        <f aca="false">IF($A53="Yes","- "&amp;$C53,"")</f>
+        <f aca="false">IF(AND($A53="Yes",$C53&lt;&gt;""),"- "&amp;$C53,"")</f>
+        <v/>
+      </c>
+      <c r="G53" s="0" t="str">
+        <f aca="false">IF($A53="Yes","- "&amp;$D53,"")</f>
         <v/>
       </c>
     </row>
@@ -5813,7 +5946,11 @@
         <v>135</v>
       </c>
       <c r="F54" s="0" t="str">
-        <f aca="false">IF($A54="Yes","- "&amp;$C54,"")</f>
+        <f aca="false">IF(AND($A54="Yes",$C54&lt;&gt;""),"- "&amp;$C54,"")</f>
+        <v/>
+      </c>
+      <c r="G54" s="0" t="str">
+        <f aca="false">IF($A54="Yes","- "&amp;$D54,"")</f>
         <v/>
       </c>
     </row>
@@ -5831,7 +5968,11 @@
         <v>138</v>
       </c>
       <c r="F55" s="0" t="str">
-        <f aca="false">IF($A55="Yes","- "&amp;$C55,"")</f>
+        <f aca="false">IF(AND($A55="Yes",$C55&lt;&gt;""),"- "&amp;$C55,"")</f>
+        <v/>
+      </c>
+      <c r="G55" s="0" t="str">
+        <f aca="false">IF($A55="Yes","- "&amp;$D55,"")</f>
         <v/>
       </c>
     </row>
@@ -5849,7 +5990,11 @@
         <v>141</v>
       </c>
       <c r="F56" s="0" t="str">
-        <f aca="false">IF($A56="Yes","- "&amp;$C56,"")</f>
+        <f aca="false">IF(AND($A56="Yes",$C56&lt;&gt;""),"- "&amp;$C56,"")</f>
+        <v/>
+      </c>
+      <c r="G56" s="0" t="str">
+        <f aca="false">IF($A56="Yes","- "&amp;$D56,"")</f>
         <v/>
       </c>
     </row>
@@ -5867,7 +6012,11 @@
         <v>144</v>
       </c>
       <c r="F57" s="0" t="str">
-        <f aca="false">IF($A57="Yes","- "&amp;$C57,"")</f>
+        <f aca="false">IF(AND($A57="Yes",$C57&lt;&gt;""),"- "&amp;$C57,"")</f>
+        <v/>
+      </c>
+      <c r="G57" s="0" t="str">
+        <f aca="false">IF($A57="Yes","- "&amp;$D57,"")</f>
         <v/>
       </c>
     </row>
@@ -5885,7 +6034,11 @@
         <v>147</v>
       </c>
       <c r="F58" s="0" t="str">
-        <f aca="false">IF($A58="Yes","- "&amp;$C58,"")</f>
+        <f aca="false">IF(AND($A58="Yes",$C58&lt;&gt;""),"- "&amp;$C58,"")</f>
+        <v/>
+      </c>
+      <c r="G58" s="0" t="str">
+        <f aca="false">IF($A58="Yes","- "&amp;$D58,"")</f>
         <v/>
       </c>
     </row>
@@ -5903,7 +6056,11 @@
         <v>150</v>
       </c>
       <c r="F59" s="0" t="str">
-        <f aca="false">IF($A59="Yes","- "&amp;$C59,"")</f>
+        <f aca="false">IF(AND($A59="Yes",$C59&lt;&gt;""),"- "&amp;$C59,"")</f>
+        <v/>
+      </c>
+      <c r="G59" s="0" t="str">
+        <f aca="false">IF($A59="Yes","- "&amp;$D59,"")</f>
         <v/>
       </c>
     </row>
@@ -5921,7 +6078,11 @@
         <v>153</v>
       </c>
       <c r="F60" s="0" t="str">
-        <f aca="false">IF($A60="Yes","- "&amp;$C60,"")</f>
+        <f aca="false">IF(AND($A60="Yes",$C60&lt;&gt;""),"- "&amp;$C60,"")</f>
+        <v/>
+      </c>
+      <c r="G60" s="0" t="str">
+        <f aca="false">IF($A60="Yes","- "&amp;$D60,"")</f>
         <v/>
       </c>
     </row>
@@ -5931,12 +6092,12 @@
       </c>
       <c r="C61" s="13"/>
     </row>
-    <row r="62" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="14" t="s">
         <v>66</v>
       </c>
       <c r="E62" s="8" t="str">
-        <f aca="false">C46&amp;IF(COUNTIF(A48:A60,"Yes")&gt;0,CHAR(10)&amp;CHAR(10)&amp;"Requirements:"&amp;CHAR(10)&amp;_xlfn.TEXTJOIN(CHAR(10),TRUE(),F48:F60),"")&amp;IF(C61&lt;&gt;"",CHAR(10)&amp;CHAR(10)&amp;"Also:"&amp;CHAR(10)&amp;C61,"")</f>
+        <f aca="false">_xlfn.TEXTJOIN(CHAR(10)&amp;CHAR(10),TRUE(),C46,IF(_xlfn.TEXTJOIN(CHAR(10),TRUE(),F48:F60)="","","Requirements:"&amp;CHAR(10)&amp;_xlfn.TEXTJOIN(CHAR(10),TRUE(),F48:F60)),IF(C61="","","Also:"&amp;CHAR(10)&amp;C61),IF(_xlfn.TEXTJOIN(CHAR(10),TRUE(),G48:G60)="","","How I will check the result:"&amp;CHAR(10)&amp;_xlfn.TEXTJOIN(CHAR(10),TRUE(),G48:G60)))</f>
         <v>A [n]-slide deck for [audience] to decide [decision], using only [verified source].</v>
       </c>
     </row>
@@ -5993,7 +6154,11 @@
         <v>159</v>
       </c>
       <c r="F68" s="0" t="str">
-        <f aca="false">IF($A68="Yes","- "&amp;$C68,"")</f>
+        <f aca="false">IF(AND($A68="Yes",$C68&lt;&gt;""),"- "&amp;$C68,"")</f>
+        <v/>
+      </c>
+      <c r="G68" s="0" t="str">
+        <f aca="false">IF($A68="Yes","- "&amp;$D68,"")</f>
         <v/>
       </c>
     </row>
@@ -6011,7 +6176,11 @@
         <v>162</v>
       </c>
       <c r="F69" s="0" t="str">
-        <f aca="false">IF($A69="Yes","- "&amp;$C69,"")</f>
+        <f aca="false">IF(AND($A69="Yes",$C69&lt;&gt;""),"- "&amp;$C69,"")</f>
+        <v/>
+      </c>
+      <c r="G69" s="0" t="str">
+        <f aca="false">IF($A69="Yes","- "&amp;$D69,"")</f>
         <v/>
       </c>
     </row>
@@ -6029,7 +6198,11 @@
         <v>165</v>
       </c>
       <c r="F70" s="0" t="str">
-        <f aca="false">IF($A70="Yes","- "&amp;$C70,"")</f>
+        <f aca="false">IF(AND($A70="Yes",$C70&lt;&gt;""),"- "&amp;$C70,"")</f>
+        <v/>
+      </c>
+      <c r="G70" s="0" t="str">
+        <f aca="false">IF($A70="Yes","- "&amp;$D70,"")</f>
         <v/>
       </c>
     </row>
@@ -6047,7 +6220,11 @@
         <v>168</v>
       </c>
       <c r="F71" s="0" t="str">
-        <f aca="false">IF($A71="Yes","- "&amp;$C71,"")</f>
+        <f aca="false">IF(AND($A71="Yes",$C71&lt;&gt;""),"- "&amp;$C71,"")</f>
+        <v/>
+      </c>
+      <c r="G71" s="0" t="str">
+        <f aca="false">IF($A71="Yes","- "&amp;$D71,"")</f>
         <v/>
       </c>
     </row>
@@ -6065,7 +6242,11 @@
         <v>171</v>
       </c>
       <c r="F72" s="0" t="str">
-        <f aca="false">IF($A72="Yes","- "&amp;$C72,"")</f>
+        <f aca="false">IF(AND($A72="Yes",$C72&lt;&gt;""),"- "&amp;$C72,"")</f>
+        <v/>
+      </c>
+      <c r="G72" s="0" t="str">
+        <f aca="false">IF($A72="Yes","- "&amp;$D72,"")</f>
         <v/>
       </c>
     </row>
@@ -6083,7 +6264,11 @@
         <v>174</v>
       </c>
       <c r="F73" s="0" t="str">
-        <f aca="false">IF($A73="Yes","- "&amp;$C73,"")</f>
+        <f aca="false">IF(AND($A73="Yes",$C73&lt;&gt;""),"- "&amp;$C73,"")</f>
+        <v/>
+      </c>
+      <c r="G73" s="0" t="str">
+        <f aca="false">IF($A73="Yes","- "&amp;$D73,"")</f>
         <v/>
       </c>
     </row>
@@ -6101,7 +6286,11 @@
         <v>177</v>
       </c>
       <c r="F74" s="0" t="str">
-        <f aca="false">IF($A74="Yes","- "&amp;$C74,"")</f>
+        <f aca="false">IF(AND($A74="Yes",$C74&lt;&gt;""),"- "&amp;$C74,"")</f>
+        <v/>
+      </c>
+      <c r="G74" s="0" t="str">
+        <f aca="false">IF($A74="Yes","- "&amp;$D74,"")</f>
         <v/>
       </c>
     </row>
@@ -6119,7 +6308,11 @@
         <v>180</v>
       </c>
       <c r="F75" s="0" t="str">
-        <f aca="false">IF($A75="Yes","- "&amp;$C75,"")</f>
+        <f aca="false">IF(AND($A75="Yes",$C75&lt;&gt;""),"- "&amp;$C75,"")</f>
+        <v/>
+      </c>
+      <c r="G75" s="0" t="str">
+        <f aca="false">IF($A75="Yes","- "&amp;$D75,"")</f>
         <v/>
       </c>
     </row>
@@ -6137,7 +6330,11 @@
         <v>183</v>
       </c>
       <c r="F76" s="0" t="str">
-        <f aca="false">IF($A76="Yes","- "&amp;$C76,"")</f>
+        <f aca="false">IF(AND($A76="Yes",$C76&lt;&gt;""),"- "&amp;$C76,"")</f>
+        <v/>
+      </c>
+      <c r="G76" s="0" t="str">
+        <f aca="false">IF($A76="Yes","- "&amp;$D76,"")</f>
         <v/>
       </c>
     </row>
@@ -6155,7 +6352,11 @@
         <v>186</v>
       </c>
       <c r="F77" s="0" t="str">
-        <f aca="false">IF($A77="Yes","- "&amp;$C77,"")</f>
+        <f aca="false">IF(AND($A77="Yes",$C77&lt;&gt;""),"- "&amp;$C77,"")</f>
+        <v/>
+      </c>
+      <c r="G77" s="0" t="str">
+        <f aca="false">IF($A77="Yes","- "&amp;$D77,"")</f>
         <v/>
       </c>
     </row>
@@ -6173,7 +6374,11 @@
         <v>189</v>
       </c>
       <c r="F78" s="0" t="str">
-        <f aca="false">IF($A78="Yes","- "&amp;$C78,"")</f>
+        <f aca="false">IF(AND($A78="Yes",$C78&lt;&gt;""),"- "&amp;$C78,"")</f>
+        <v/>
+      </c>
+      <c r="G78" s="0" t="str">
+        <f aca="false">IF($A78="Yes","- "&amp;$D78,"")</f>
         <v/>
       </c>
     </row>
@@ -6191,7 +6396,11 @@
         <v>192</v>
       </c>
       <c r="F79" s="0" t="str">
-        <f aca="false">IF($A79="Yes","- "&amp;$C79,"")</f>
+        <f aca="false">IF(AND($A79="Yes",$C79&lt;&gt;""),"- "&amp;$C79,"")</f>
+        <v/>
+      </c>
+      <c r="G79" s="0" t="str">
+        <f aca="false">IF($A79="Yes","- "&amp;$D79,"")</f>
         <v/>
       </c>
     </row>
@@ -6201,12 +6410,12 @@
       </c>
       <c r="C80" s="13"/>
     </row>
-    <row r="81" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="14" t="s">
         <v>66</v>
       </c>
       <c r="E81" s="8" t="str">
-        <f aca="false">C66&amp;IF(COUNTIF(A68:A79,"Yes")&gt;0,CHAR(10)&amp;CHAR(10)&amp;"Requirements:"&amp;CHAR(10)&amp;_xlfn.TEXTJOIN(CHAR(10),TRUE(),F68:F79),"")&amp;IF(C80&lt;&gt;"",CHAR(10)&amp;CHAR(10)&amp;"Also:"&amp;CHAR(10)&amp;C80,"")</f>
+        <f aca="false">_xlfn.TEXTJOIN(CHAR(10)&amp;CHAR(10),TRUE(),C66,IF(_xlfn.TEXTJOIN(CHAR(10),TRUE(),F68:F79)="","","Requirements:"&amp;CHAR(10)&amp;_xlfn.TEXTJOIN(CHAR(10),TRUE(),F68:F79)),IF(C80="","","Also:"&amp;CHAR(10)&amp;C80),IF(_xlfn.TEXTJOIN(CHAR(10),TRUE(),G68:G79)="","","How I will check the result:"&amp;CHAR(10)&amp;_xlfn.TEXTJOIN(CHAR(10),TRUE(),G68:G79)))</f>
         <v>Brief the conversation about [topic] so [reader] knows the current state and what they owe.</v>
       </c>
     </row>
@@ -6263,7 +6472,11 @@
         <v>198</v>
       </c>
       <c r="F87" s="0" t="str">
-        <f aca="false">IF($A87="Yes","- "&amp;$C87,"")</f>
+        <f aca="false">IF(AND($A87="Yes",$C87&lt;&gt;""),"- "&amp;$C87,"")</f>
+        <v/>
+      </c>
+      <c r="G87" s="0" t="str">
+        <f aca="false">IF($A87="Yes","- "&amp;$D87,"")</f>
         <v/>
       </c>
     </row>
@@ -6281,7 +6494,11 @@
         <v>201</v>
       </c>
       <c r="F88" s="0" t="str">
-        <f aca="false">IF($A88="Yes","- "&amp;$C88,"")</f>
+        <f aca="false">IF(AND($A88="Yes",$C88&lt;&gt;""),"- "&amp;$C88,"")</f>
+        <v/>
+      </c>
+      <c r="G88" s="0" t="str">
+        <f aca="false">IF($A88="Yes","- "&amp;$D88,"")</f>
         <v/>
       </c>
     </row>
@@ -6299,7 +6516,11 @@
         <v>204</v>
       </c>
       <c r="F89" s="0" t="str">
-        <f aca="false">IF($A89="Yes","- "&amp;$C89,"")</f>
+        <f aca="false">IF(AND($A89="Yes",$C89&lt;&gt;""),"- "&amp;$C89,"")</f>
+        <v/>
+      </c>
+      <c r="G89" s="0" t="str">
+        <f aca="false">IF($A89="Yes","- "&amp;$D89,"")</f>
         <v/>
       </c>
     </row>
@@ -6317,7 +6538,11 @@
         <v>207</v>
       </c>
       <c r="F90" s="0" t="str">
-        <f aca="false">IF($A90="Yes","- "&amp;$C90,"")</f>
+        <f aca="false">IF(AND($A90="Yes",$C90&lt;&gt;""),"- "&amp;$C90,"")</f>
+        <v/>
+      </c>
+      <c r="G90" s="0" t="str">
+        <f aca="false">IF($A90="Yes","- "&amp;$D90,"")</f>
         <v/>
       </c>
     </row>
@@ -6335,7 +6560,11 @@
         <v>210</v>
       </c>
       <c r="F91" s="0" t="str">
-        <f aca="false">IF($A91="Yes","- "&amp;$C91,"")</f>
+        <f aca="false">IF(AND($A91="Yes",$C91&lt;&gt;""),"- "&amp;$C91,"")</f>
+        <v/>
+      </c>
+      <c r="G91" s="0" t="str">
+        <f aca="false">IF($A91="Yes","- "&amp;$D91,"")</f>
         <v/>
       </c>
     </row>
@@ -6353,7 +6582,11 @@
         <v>213</v>
       </c>
       <c r="F92" s="0" t="str">
-        <f aca="false">IF($A92="Yes","- "&amp;$C92,"")</f>
+        <f aca="false">IF(AND($A92="Yes",$C92&lt;&gt;""),"- "&amp;$C92,"")</f>
+        <v/>
+      </c>
+      <c r="G92" s="0" t="str">
+        <f aca="false">IF($A92="Yes","- "&amp;$D92,"")</f>
         <v/>
       </c>
     </row>
@@ -6371,7 +6604,11 @@
         <v>216</v>
       </c>
       <c r="F93" s="0" t="str">
-        <f aca="false">IF($A93="Yes","- "&amp;$C93,"")</f>
+        <f aca="false">IF(AND($A93="Yes",$C93&lt;&gt;""),"- "&amp;$C93,"")</f>
+        <v/>
+      </c>
+      <c r="G93" s="0" t="str">
+        <f aca="false">IF($A93="Yes","- "&amp;$D93,"")</f>
         <v/>
       </c>
     </row>
@@ -6389,7 +6626,11 @@
         <v>219</v>
       </c>
       <c r="F94" s="0" t="str">
-        <f aca="false">IF($A94="Yes","- "&amp;$C94,"")</f>
+        <f aca="false">IF(AND($A94="Yes",$C94&lt;&gt;""),"- "&amp;$C94,"")</f>
+        <v/>
+      </c>
+      <c r="G94" s="0" t="str">
+        <f aca="false">IF($A94="Yes","- "&amp;$D94,"")</f>
         <v/>
       </c>
     </row>
@@ -6407,7 +6648,11 @@
         <v>222</v>
       </c>
       <c r="F95" s="0" t="str">
-        <f aca="false">IF($A95="Yes","- "&amp;$C95,"")</f>
+        <f aca="false">IF(AND($A95="Yes",$C95&lt;&gt;""),"- "&amp;$C95,"")</f>
+        <v/>
+      </c>
+      <c r="G95" s="0" t="str">
+        <f aca="false">IF($A95="Yes","- "&amp;$D95,"")</f>
         <v/>
       </c>
     </row>
@@ -6425,7 +6670,11 @@
         <v>225</v>
       </c>
       <c r="F96" s="0" t="str">
-        <f aca="false">IF($A96="Yes","- "&amp;$C96,"")</f>
+        <f aca="false">IF(AND($A96="Yes",$C96&lt;&gt;""),"- "&amp;$C96,"")</f>
+        <v/>
+      </c>
+      <c r="G96" s="0" t="str">
+        <f aca="false">IF($A96="Yes","- "&amp;$D96,"")</f>
         <v/>
       </c>
     </row>
@@ -6443,7 +6692,11 @@
         <v>228</v>
       </c>
       <c r="F97" s="0" t="str">
-        <f aca="false">IF($A97="Yes","- "&amp;$C97,"")</f>
+        <f aca="false">IF(AND($A97="Yes",$C97&lt;&gt;""),"- "&amp;$C97,"")</f>
+        <v/>
+      </c>
+      <c r="G97" s="0" t="str">
+        <f aca="false">IF($A97="Yes","- "&amp;$D97,"")</f>
         <v/>
       </c>
     </row>
@@ -6461,7 +6714,11 @@
         <v>231</v>
       </c>
       <c r="F98" s="0" t="str">
-        <f aca="false">IF($A98="Yes","- "&amp;$C98,"")</f>
+        <f aca="false">IF(AND($A98="Yes",$C98&lt;&gt;""),"- "&amp;$C98,"")</f>
+        <v/>
+      </c>
+      <c r="G98" s="0" t="str">
+        <f aca="false">IF($A98="Yes","- "&amp;$D98,"")</f>
         <v/>
       </c>
     </row>
@@ -6479,7 +6736,11 @@
         <v>234</v>
       </c>
       <c r="F99" s="0" t="str">
-        <f aca="false">IF($A99="Yes","- "&amp;$C99,"")</f>
+        <f aca="false">IF(AND($A99="Yes",$C99&lt;&gt;""),"- "&amp;$C99,"")</f>
+        <v/>
+      </c>
+      <c r="G99" s="0" t="str">
+        <f aca="false">IF($A99="Yes","- "&amp;$D99,"")</f>
         <v/>
       </c>
     </row>
@@ -6489,12 +6750,12 @@
       </c>
       <c r="C100" s="13"/>
     </row>
-    <row r="101" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B101" s="14" t="s">
         <v>66</v>
       </c>
       <c r="E101" s="8" t="str">
-        <f aca="false">C85&amp;IF(COUNTIF(A87:A99,"Yes")&gt;0,CHAR(10)&amp;CHAR(10)&amp;"Requirements:"&amp;CHAR(10)&amp;_xlfn.TEXTJOIN(CHAR(10),TRUE(),F87:F99),"")&amp;IF(C100&lt;&gt;"",CHAR(10)&amp;CHAR(10)&amp;"Also:"&amp;CHAR(10)&amp;C100,"")</f>
+        <f aca="false">_xlfn.TEXTJOIN(CHAR(10)&amp;CHAR(10),TRUE(),C85,IF(_xlfn.TEXTJOIN(CHAR(10),TRUE(),F87:F99)="","","Requirements:"&amp;CHAR(10)&amp;_xlfn.TEXTJOIN(CHAR(10),TRUE(),F87:F99)),IF(C100="","","Also:"&amp;CHAR(10)&amp;C100),IF(_xlfn.TEXTJOIN(CHAR(10),TRUE(),G87:G99)="","","How I will check the result:"&amp;CHAR(10)&amp;_xlfn.TEXTJOIN(CHAR(10),TRUE(),G87:G99)))</f>
         <v>Explain [topic] from [source] for a reader at [reading level] who needs to [do / understand].</v>
       </c>
     </row>

--- a/ai-training-prompt-engineering/references/Prompt_Template_Configurator.xlsx
+++ b/ai-training-prompt-engineering/references/Prompt_Template_Configurator.xlsx
@@ -5068,7 +5068,7 @@
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
     </row>
-    <row r="4" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="139.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
         <v>17</v>
       </c>
@@ -5112,7 +5112,7 @@
         <v>28</v>
       </c>
       <c r="F7" s="0" t="str">
-        <f aca="false">IF(AND($A7="Yes",$C7&lt;&gt;""),"- "&amp;$C7,"")</f>
+        <f aca="false">IF(AND($A7="Yes",TRIM($C7)&lt;&gt;""),"- "&amp;TRIM($C7),"")</f>
         <v/>
       </c>
       <c r="G7" s="0" t="str">
@@ -5134,7 +5134,7 @@
         <v>31</v>
       </c>
       <c r="F8" s="0" t="str">
-        <f aca="false">IF(AND($A8="Yes",$C8&lt;&gt;""),"- "&amp;$C8,"")</f>
+        <f aca="false">IF(AND($A8="Yes",TRIM($C8)&lt;&gt;""),"- "&amp;TRIM($C8),"")</f>
         <v/>
       </c>
       <c r="G8" s="0" t="str">
@@ -5156,7 +5156,7 @@
         <v>34</v>
       </c>
       <c r="F9" s="0" t="str">
-        <f aca="false">IF(AND($A9="Yes",$C9&lt;&gt;""),"- "&amp;$C9,"")</f>
+        <f aca="false">IF(AND($A9="Yes",TRIM($C9)&lt;&gt;""),"- "&amp;TRIM($C9),"")</f>
         <v/>
       </c>
       <c r="G9" s="0" t="str">
@@ -5178,7 +5178,7 @@
         <v>37</v>
       </c>
       <c r="F10" s="0" t="str">
-        <f aca="false">IF(AND($A10="Yes",$C10&lt;&gt;""),"- "&amp;$C10,"")</f>
+        <f aca="false">IF(AND($A10="Yes",TRIM($C10)&lt;&gt;""),"- "&amp;TRIM($C10),"")</f>
         <v/>
       </c>
       <c r="G10" s="0" t="str">
@@ -5200,7 +5200,7 @@
         <v>40</v>
       </c>
       <c r="F11" s="0" t="str">
-        <f aca="false">IF(AND($A11="Yes",$C11&lt;&gt;""),"- "&amp;$C11,"")</f>
+        <f aca="false">IF(AND($A11="Yes",TRIM($C11)&lt;&gt;""),"- "&amp;TRIM($C11),"")</f>
         <v/>
       </c>
       <c r="G11" s="0" t="str">
@@ -5222,7 +5222,7 @@
         <v>43</v>
       </c>
       <c r="F12" s="0" t="str">
-        <f aca="false">IF(AND($A12="Yes",$C12&lt;&gt;""),"- "&amp;$C12,"")</f>
+        <f aca="false">IF(AND($A12="Yes",TRIM($C12)&lt;&gt;""),"- "&amp;TRIM($C12),"")</f>
         <v/>
       </c>
       <c r="G12" s="0" t="str">
@@ -5244,7 +5244,7 @@
         <v>46</v>
       </c>
       <c r="F13" s="0" t="str">
-        <f aca="false">IF(AND($A13="Yes",$C13&lt;&gt;""),"- "&amp;$C13,"")</f>
+        <f aca="false">IF(AND($A13="Yes",TRIM($C13)&lt;&gt;""),"- "&amp;TRIM($C13),"")</f>
         <v/>
       </c>
       <c r="G13" s="0" t="str">
@@ -5266,7 +5266,7 @@
         <v>49</v>
       </c>
       <c r="F14" s="0" t="str">
-        <f aca="false">IF(AND($A14="Yes",$C14&lt;&gt;""),"- "&amp;$C14,"")</f>
+        <f aca="false">IF(AND($A14="Yes",TRIM($C14)&lt;&gt;""),"- "&amp;TRIM($C14),"")</f>
         <v/>
       </c>
       <c r="G14" s="0" t="str">
@@ -5288,7 +5288,7 @@
         <v>52</v>
       </c>
       <c r="F15" s="0" t="str">
-        <f aca="false">IF(AND($A15="Yes",$C15&lt;&gt;""),"- "&amp;$C15,"")</f>
+        <f aca="false">IF(AND($A15="Yes",TRIM($C15)&lt;&gt;""),"- "&amp;TRIM($C15),"")</f>
         <v/>
       </c>
       <c r="G15" s="0" t="str">
@@ -5310,7 +5310,7 @@
         <v>55</v>
       </c>
       <c r="F16" s="0" t="str">
-        <f aca="false">IF(AND($A16="Yes",$C16&lt;&gt;""),"- "&amp;$C16,"")</f>
+        <f aca="false">IF(AND($A16="Yes",TRIM($C16)&lt;&gt;""),"- "&amp;TRIM($C16),"")</f>
         <v/>
       </c>
       <c r="G16" s="0" t="str">
@@ -5332,7 +5332,7 @@
         <v>58</v>
       </c>
       <c r="F17" s="0" t="str">
-        <f aca="false">IF(AND($A17="Yes",$C17&lt;&gt;""),"- "&amp;$C17,"")</f>
+        <f aca="false">IF(AND($A17="Yes",TRIM($C17)&lt;&gt;""),"- "&amp;TRIM($C17),"")</f>
         <v/>
       </c>
       <c r="G17" s="0" t="str">
@@ -5354,7 +5354,7 @@
         <v>61</v>
       </c>
       <c r="F18" s="0" t="str">
-        <f aca="false">IF(AND($A18="Yes",$C18&lt;&gt;""),"- "&amp;$C18,"")</f>
+        <f aca="false">IF(AND($A18="Yes",TRIM($C18)&lt;&gt;""),"- "&amp;TRIM($C18),"")</f>
         <v/>
       </c>
       <c r="G18" s="0" t="str">
@@ -5376,7 +5376,7 @@
         <v>64</v>
       </c>
       <c r="F19" s="0" t="str">
-        <f aca="false">IF(AND($A19="Yes",$C19&lt;&gt;""),"- "&amp;$C19,"")</f>
+        <f aca="false">IF(AND($A19="Yes",TRIM($C19)&lt;&gt;""),"- "&amp;TRIM($C19),"")</f>
         <v/>
       </c>
       <c r="G19" s="0" t="str">
@@ -5408,7 +5408,7 @@
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
     </row>
-    <row r="24" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="7" t="s">
         <v>17</v>
       </c>
@@ -5452,7 +5452,7 @@
         <v>72</v>
       </c>
       <c r="F27" s="0" t="str">
-        <f aca="false">IF(AND($A27="Yes",$C27&lt;&gt;""),"- "&amp;$C27,"")</f>
+        <f aca="false">IF(AND($A27="Yes",TRIM($C27)&lt;&gt;""),"- "&amp;TRIM($C27),"")</f>
         <v/>
       </c>
       <c r="G27" s="0" t="str">
@@ -5474,7 +5474,7 @@
         <v>75</v>
       </c>
       <c r="F28" s="0" t="str">
-        <f aca="false">IF(AND($A28="Yes",$C28&lt;&gt;""),"- "&amp;$C28,"")</f>
+        <f aca="false">IF(AND($A28="Yes",TRIM($C28)&lt;&gt;""),"- "&amp;TRIM($C28),"")</f>
         <v/>
       </c>
       <c r="G28" s="0" t="str">
@@ -5496,7 +5496,7 @@
         <v>78</v>
       </c>
       <c r="F29" s="0" t="str">
-        <f aca="false">IF(AND($A29="Yes",$C29&lt;&gt;""),"- "&amp;$C29,"")</f>
+        <f aca="false">IF(AND($A29="Yes",TRIM($C29)&lt;&gt;""),"- "&amp;TRIM($C29),"")</f>
         <v/>
       </c>
       <c r="G29" s="0" t="str">
@@ -5518,7 +5518,7 @@
         <v>81</v>
       </c>
       <c r="F30" s="0" t="str">
-        <f aca="false">IF(AND($A30="Yes",$C30&lt;&gt;""),"- "&amp;$C30,"")</f>
+        <f aca="false">IF(AND($A30="Yes",TRIM($C30)&lt;&gt;""),"- "&amp;TRIM($C30),"")</f>
         <v/>
       </c>
       <c r="G30" s="0" t="str">
@@ -5540,7 +5540,7 @@
         <v>84</v>
       </c>
       <c r="F31" s="0" t="str">
-        <f aca="false">IF(AND($A31="Yes",$C31&lt;&gt;""),"- "&amp;$C31,"")</f>
+        <f aca="false">IF(AND($A31="Yes",TRIM($C31)&lt;&gt;""),"- "&amp;TRIM($C31),"")</f>
         <v/>
       </c>
       <c r="G31" s="0" t="str">
@@ -5562,7 +5562,7 @@
         <v>87</v>
       </c>
       <c r="F32" s="0" t="str">
-        <f aca="false">IF(AND($A32="Yes",$C32&lt;&gt;""),"- "&amp;$C32,"")</f>
+        <f aca="false">IF(AND($A32="Yes",TRIM($C32)&lt;&gt;""),"- "&amp;TRIM($C32),"")</f>
         <v/>
       </c>
       <c r="G32" s="0" t="str">
@@ -5584,7 +5584,7 @@
         <v>90</v>
       </c>
       <c r="F33" s="0" t="str">
-        <f aca="false">IF(AND($A33="Yes",$C33&lt;&gt;""),"- "&amp;$C33,"")</f>
+        <f aca="false">IF(AND($A33="Yes",TRIM($C33)&lt;&gt;""),"- "&amp;TRIM($C33),"")</f>
         <v/>
       </c>
       <c r="G33" s="0" t="str">
@@ -5606,7 +5606,7 @@
         <v>93</v>
       </c>
       <c r="F34" s="0" t="str">
-        <f aca="false">IF(AND($A34="Yes",$C34&lt;&gt;""),"- "&amp;$C34,"")</f>
+        <f aca="false">IF(AND($A34="Yes",TRIM($C34)&lt;&gt;""),"- "&amp;TRIM($C34),"")</f>
         <v/>
       </c>
       <c r="G34" s="0" t="str">
@@ -5628,7 +5628,7 @@
         <v>96</v>
       </c>
       <c r="F35" s="0" t="str">
-        <f aca="false">IF(AND($A35="Yes",$C35&lt;&gt;""),"- "&amp;$C35,"")</f>
+        <f aca="false">IF(AND($A35="Yes",TRIM($C35)&lt;&gt;""),"- "&amp;TRIM($C35),"")</f>
         <v/>
       </c>
       <c r="G35" s="0" t="str">
@@ -5650,7 +5650,7 @@
         <v>99</v>
       </c>
       <c r="F36" s="0" t="str">
-        <f aca="false">IF(AND($A36="Yes",$C36&lt;&gt;""),"- "&amp;$C36,"")</f>
+        <f aca="false">IF(AND($A36="Yes",TRIM($C36)&lt;&gt;""),"- "&amp;TRIM($C36),"")</f>
         <v/>
       </c>
       <c r="G36" s="0" t="str">
@@ -5672,7 +5672,7 @@
         <v>102</v>
       </c>
       <c r="F37" s="0" t="str">
-        <f aca="false">IF(AND($A37="Yes",$C37&lt;&gt;""),"- "&amp;$C37,"")</f>
+        <f aca="false">IF(AND($A37="Yes",TRIM($C37)&lt;&gt;""),"- "&amp;TRIM($C37),"")</f>
         <v/>
       </c>
       <c r="G37" s="0" t="str">
@@ -5694,7 +5694,7 @@
         <v>105</v>
       </c>
       <c r="F38" s="0" t="str">
-        <f aca="false">IF(AND($A38="Yes",$C38&lt;&gt;""),"- "&amp;$C38,"")</f>
+        <f aca="false">IF(AND($A38="Yes",TRIM($C38)&lt;&gt;""),"- "&amp;TRIM($C38),"")</f>
         <v/>
       </c>
       <c r="G38" s="0" t="str">
@@ -5716,7 +5716,7 @@
         <v>108</v>
       </c>
       <c r="F39" s="0" t="str">
-        <f aca="false">IF(AND($A39="Yes",$C39&lt;&gt;""),"- "&amp;$C39,"")</f>
+        <f aca="false">IF(AND($A39="Yes",TRIM($C39)&lt;&gt;""),"- "&amp;TRIM($C39),"")</f>
         <v/>
       </c>
       <c r="G39" s="0" t="str">
@@ -5738,7 +5738,7 @@
         <v>111</v>
       </c>
       <c r="F40" s="0" t="str">
-        <f aca="false">IF(AND($A40="Yes",$C40&lt;&gt;""),"- "&amp;$C40,"")</f>
+        <f aca="false">IF(AND($A40="Yes",TRIM($C40)&lt;&gt;""),"- "&amp;TRIM($C40),"")</f>
         <v/>
       </c>
       <c r="G40" s="0" t="str">
@@ -5770,7 +5770,7 @@
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
     </row>
-    <row r="45" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="7" t="s">
         <v>17</v>
       </c>
@@ -5814,7 +5814,7 @@
         <v>117</v>
       </c>
       <c r="F48" s="0" t="str">
-        <f aca="false">IF(AND($A48="Yes",$C48&lt;&gt;""),"- "&amp;$C48,"")</f>
+        <f aca="false">IF(AND($A48="Yes",TRIM($C48)&lt;&gt;""),"- "&amp;TRIM($C48),"")</f>
         <v/>
       </c>
       <c r="G48" s="0" t="str">
@@ -5836,7 +5836,7 @@
         <v>120</v>
       </c>
       <c r="F49" s="0" t="str">
-        <f aca="false">IF(AND($A49="Yes",$C49&lt;&gt;""),"- "&amp;$C49,"")</f>
+        <f aca="false">IF(AND($A49="Yes",TRIM($C49)&lt;&gt;""),"- "&amp;TRIM($C49),"")</f>
         <v/>
       </c>
       <c r="G49" s="0" t="str">
@@ -5858,7 +5858,7 @@
         <v>123</v>
       </c>
       <c r="F50" s="0" t="str">
-        <f aca="false">IF(AND($A50="Yes",$C50&lt;&gt;""),"- "&amp;$C50,"")</f>
+        <f aca="false">IF(AND($A50="Yes",TRIM($C50)&lt;&gt;""),"- "&amp;TRIM($C50),"")</f>
         <v/>
       </c>
       <c r="G50" s="0" t="str">
@@ -5880,7 +5880,7 @@
         <v>126</v>
       </c>
       <c r="F51" s="0" t="str">
-        <f aca="false">IF(AND($A51="Yes",$C51&lt;&gt;""),"- "&amp;$C51,"")</f>
+        <f aca="false">IF(AND($A51="Yes",TRIM($C51)&lt;&gt;""),"- "&amp;TRIM($C51),"")</f>
         <v/>
       </c>
       <c r="G51" s="0" t="str">
@@ -5902,7 +5902,7 @@
         <v>129</v>
       </c>
       <c r="F52" s="0" t="str">
-        <f aca="false">IF(AND($A52="Yes",$C52&lt;&gt;""),"- "&amp;$C52,"")</f>
+        <f aca="false">IF(AND($A52="Yes",TRIM($C52)&lt;&gt;""),"- "&amp;TRIM($C52),"")</f>
         <v/>
       </c>
       <c r="G52" s="0" t="str">
@@ -5924,7 +5924,7 @@
         <v>132</v>
       </c>
       <c r="F53" s="0" t="str">
-        <f aca="false">IF(AND($A53="Yes",$C53&lt;&gt;""),"- "&amp;$C53,"")</f>
+        <f aca="false">IF(AND($A53="Yes",TRIM($C53)&lt;&gt;""),"- "&amp;TRIM($C53),"")</f>
         <v/>
       </c>
       <c r="G53" s="0" t="str">
@@ -5946,7 +5946,7 @@
         <v>135</v>
       </c>
       <c r="F54" s="0" t="str">
-        <f aca="false">IF(AND($A54="Yes",$C54&lt;&gt;""),"- "&amp;$C54,"")</f>
+        <f aca="false">IF(AND($A54="Yes",TRIM($C54)&lt;&gt;""),"- "&amp;TRIM($C54),"")</f>
         <v/>
       </c>
       <c r="G54" s="0" t="str">
@@ -5968,7 +5968,7 @@
         <v>138</v>
       </c>
       <c r="F55" s="0" t="str">
-        <f aca="false">IF(AND($A55="Yes",$C55&lt;&gt;""),"- "&amp;$C55,"")</f>
+        <f aca="false">IF(AND($A55="Yes",TRIM($C55)&lt;&gt;""),"- "&amp;TRIM($C55),"")</f>
         <v/>
       </c>
       <c r="G55" s="0" t="str">
@@ -5990,7 +5990,7 @@
         <v>141</v>
       </c>
       <c r="F56" s="0" t="str">
-        <f aca="false">IF(AND($A56="Yes",$C56&lt;&gt;""),"- "&amp;$C56,"")</f>
+        <f aca="false">IF(AND($A56="Yes",TRIM($C56)&lt;&gt;""),"- "&amp;TRIM($C56),"")</f>
         <v/>
       </c>
       <c r="G56" s="0" t="str">
@@ -6012,7 +6012,7 @@
         <v>144</v>
       </c>
       <c r="F57" s="0" t="str">
-        <f aca="false">IF(AND($A57="Yes",$C57&lt;&gt;""),"- "&amp;$C57,"")</f>
+        <f aca="false">IF(AND($A57="Yes",TRIM($C57)&lt;&gt;""),"- "&amp;TRIM($C57),"")</f>
         <v/>
       </c>
       <c r="G57" s="0" t="str">
@@ -6034,7 +6034,7 @@
         <v>147</v>
       </c>
       <c r="F58" s="0" t="str">
-        <f aca="false">IF(AND($A58="Yes",$C58&lt;&gt;""),"- "&amp;$C58,"")</f>
+        <f aca="false">IF(AND($A58="Yes",TRIM($C58)&lt;&gt;""),"- "&amp;TRIM($C58),"")</f>
         <v/>
       </c>
       <c r="G58" s="0" t="str">
@@ -6056,7 +6056,7 @@
         <v>150</v>
       </c>
       <c r="F59" s="0" t="str">
-        <f aca="false">IF(AND($A59="Yes",$C59&lt;&gt;""),"- "&amp;$C59,"")</f>
+        <f aca="false">IF(AND($A59="Yes",TRIM($C59)&lt;&gt;""),"- "&amp;TRIM($C59),"")</f>
         <v/>
       </c>
       <c r="G59" s="0" t="str">
@@ -6078,7 +6078,7 @@
         <v>153</v>
       </c>
       <c r="F60" s="0" t="str">
-        <f aca="false">IF(AND($A60="Yes",$C60&lt;&gt;""),"- "&amp;$C60,"")</f>
+        <f aca="false">IF(AND($A60="Yes",TRIM($C60)&lt;&gt;""),"- "&amp;TRIM($C60),"")</f>
         <v/>
       </c>
       <c r="G60" s="0" t="str">
@@ -6110,7 +6110,7 @@
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
     </row>
-    <row r="65" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="139.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="7" t="s">
         <v>17</v>
       </c>
@@ -6154,7 +6154,7 @@
         <v>159</v>
       </c>
       <c r="F68" s="0" t="str">
-        <f aca="false">IF(AND($A68="Yes",$C68&lt;&gt;""),"- "&amp;$C68,"")</f>
+        <f aca="false">IF(AND($A68="Yes",TRIM($C68)&lt;&gt;""),"- "&amp;TRIM($C68),"")</f>
         <v/>
       </c>
       <c r="G68" s="0" t="str">
@@ -6176,7 +6176,7 @@
         <v>162</v>
       </c>
       <c r="F69" s="0" t="str">
-        <f aca="false">IF(AND($A69="Yes",$C69&lt;&gt;""),"- "&amp;$C69,"")</f>
+        <f aca="false">IF(AND($A69="Yes",TRIM($C69)&lt;&gt;""),"- "&amp;TRIM($C69),"")</f>
         <v/>
       </c>
       <c r="G69" s="0" t="str">
@@ -6198,7 +6198,7 @@
         <v>165</v>
       </c>
       <c r="F70" s="0" t="str">
-        <f aca="false">IF(AND($A70="Yes",$C70&lt;&gt;""),"- "&amp;$C70,"")</f>
+        <f aca="false">IF(AND($A70="Yes",TRIM($C70)&lt;&gt;""),"- "&amp;TRIM($C70),"")</f>
         <v/>
       </c>
       <c r="G70" s="0" t="str">
@@ -6220,7 +6220,7 @@
         <v>168</v>
       </c>
       <c r="F71" s="0" t="str">
-        <f aca="false">IF(AND($A71="Yes",$C71&lt;&gt;""),"- "&amp;$C71,"")</f>
+        <f aca="false">IF(AND($A71="Yes",TRIM($C71)&lt;&gt;""),"- "&amp;TRIM($C71),"")</f>
         <v/>
       </c>
       <c r="G71" s="0" t="str">
@@ -6242,7 +6242,7 @@
         <v>171</v>
       </c>
       <c r="F72" s="0" t="str">
-        <f aca="false">IF(AND($A72="Yes",$C72&lt;&gt;""),"- "&amp;$C72,"")</f>
+        <f aca="false">IF(AND($A72="Yes",TRIM($C72)&lt;&gt;""),"- "&amp;TRIM($C72),"")</f>
         <v/>
       </c>
       <c r="G72" s="0" t="str">
@@ -6264,7 +6264,7 @@
         <v>174</v>
       </c>
       <c r="F73" s="0" t="str">
-        <f aca="false">IF(AND($A73="Yes",$C73&lt;&gt;""),"- "&amp;$C73,"")</f>
+        <f aca="false">IF(AND($A73="Yes",TRIM($C73)&lt;&gt;""),"- "&amp;TRIM($C73),"")</f>
         <v/>
       </c>
       <c r="G73" s="0" t="str">
@@ -6286,7 +6286,7 @@
         <v>177</v>
       </c>
       <c r="F74" s="0" t="str">
-        <f aca="false">IF(AND($A74="Yes",$C74&lt;&gt;""),"- "&amp;$C74,"")</f>
+        <f aca="false">IF(AND($A74="Yes",TRIM($C74)&lt;&gt;""),"- "&amp;TRIM($C74),"")</f>
         <v/>
       </c>
       <c r="G74" s="0" t="str">
@@ -6308,7 +6308,7 @@
         <v>180</v>
       </c>
       <c r="F75" s="0" t="str">
-        <f aca="false">IF(AND($A75="Yes",$C75&lt;&gt;""),"- "&amp;$C75,"")</f>
+        <f aca="false">IF(AND($A75="Yes",TRIM($C75)&lt;&gt;""),"- "&amp;TRIM($C75),"")</f>
         <v/>
       </c>
       <c r="G75" s="0" t="str">
@@ -6330,7 +6330,7 @@
         <v>183</v>
       </c>
       <c r="F76" s="0" t="str">
-        <f aca="false">IF(AND($A76="Yes",$C76&lt;&gt;""),"- "&amp;$C76,"")</f>
+        <f aca="false">IF(AND($A76="Yes",TRIM($C76)&lt;&gt;""),"- "&amp;TRIM($C76),"")</f>
         <v/>
       </c>
       <c r="G76" s="0" t="str">
@@ -6352,7 +6352,7 @@
         <v>186</v>
       </c>
       <c r="F77" s="0" t="str">
-        <f aca="false">IF(AND($A77="Yes",$C77&lt;&gt;""),"- "&amp;$C77,"")</f>
+        <f aca="false">IF(AND($A77="Yes",TRIM($C77)&lt;&gt;""),"- "&amp;TRIM($C77),"")</f>
         <v/>
       </c>
       <c r="G77" s="0" t="str">
@@ -6374,7 +6374,7 @@
         <v>189</v>
       </c>
       <c r="F78" s="0" t="str">
-        <f aca="false">IF(AND($A78="Yes",$C78&lt;&gt;""),"- "&amp;$C78,"")</f>
+        <f aca="false">IF(AND($A78="Yes",TRIM($C78)&lt;&gt;""),"- "&amp;TRIM($C78),"")</f>
         <v/>
       </c>
       <c r="G78" s="0" t="str">
@@ -6396,7 +6396,7 @@
         <v>192</v>
       </c>
       <c r="F79" s="0" t="str">
-        <f aca="false">IF(AND($A79="Yes",$C79&lt;&gt;""),"- "&amp;$C79,"")</f>
+        <f aca="false">IF(AND($A79="Yes",TRIM($C79)&lt;&gt;""),"- "&amp;TRIM($C79),"")</f>
         <v/>
       </c>
       <c r="G79" s="0" t="str">
@@ -6428,7 +6428,7 @@
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
     </row>
-    <row r="84" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="7" t="s">
         <v>17</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>198</v>
       </c>
       <c r="F87" s="0" t="str">
-        <f aca="false">IF(AND($A87="Yes",$C87&lt;&gt;""),"- "&amp;$C87,"")</f>
+        <f aca="false">IF(AND($A87="Yes",TRIM($C87)&lt;&gt;""),"- "&amp;TRIM($C87),"")</f>
         <v/>
       </c>
       <c r="G87" s="0" t="str">
@@ -6494,7 +6494,7 @@
         <v>201</v>
       </c>
       <c r="F88" s="0" t="str">
-        <f aca="false">IF(AND($A88="Yes",$C88&lt;&gt;""),"- "&amp;$C88,"")</f>
+        <f aca="false">IF(AND($A88="Yes",TRIM($C88)&lt;&gt;""),"- "&amp;TRIM($C88),"")</f>
         <v/>
       </c>
       <c r="G88" s="0" t="str">
@@ -6516,7 +6516,7 @@
         <v>204</v>
       </c>
       <c r="F89" s="0" t="str">
-        <f aca="false">IF(AND($A89="Yes",$C89&lt;&gt;""),"- "&amp;$C89,"")</f>
+        <f aca="false">IF(AND($A89="Yes",TRIM($C89)&lt;&gt;""),"- "&amp;TRIM($C89),"")</f>
         <v/>
       </c>
       <c r="G89" s="0" t="str">
@@ -6538,7 +6538,7 @@
         <v>207</v>
       </c>
       <c r="F90" s="0" t="str">
-        <f aca="false">IF(AND($A90="Yes",$C90&lt;&gt;""),"- "&amp;$C90,"")</f>
+        <f aca="false">IF(AND($A90="Yes",TRIM($C90)&lt;&gt;""),"- "&amp;TRIM($C90),"")</f>
         <v/>
       </c>
       <c r="G90" s="0" t="str">
@@ -6560,7 +6560,7 @@
         <v>210</v>
       </c>
       <c r="F91" s="0" t="str">
-        <f aca="false">IF(AND($A91="Yes",$C91&lt;&gt;""),"- "&amp;$C91,"")</f>
+        <f aca="false">IF(AND($A91="Yes",TRIM($C91)&lt;&gt;""),"- "&amp;TRIM($C91),"")</f>
         <v/>
       </c>
       <c r="G91" s="0" t="str">
@@ -6582,7 +6582,7 @@
         <v>213</v>
       </c>
       <c r="F92" s="0" t="str">
-        <f aca="false">IF(AND($A92="Yes",$C92&lt;&gt;""),"- "&amp;$C92,"")</f>
+        <f aca="false">IF(AND($A92="Yes",TRIM($C92)&lt;&gt;""),"- "&amp;TRIM($C92),"")</f>
         <v/>
       </c>
       <c r="G92" s="0" t="str">
@@ -6604,7 +6604,7 @@
         <v>216</v>
       </c>
       <c r="F93" s="0" t="str">
-        <f aca="false">IF(AND($A93="Yes",$C93&lt;&gt;""),"- "&amp;$C93,"")</f>
+        <f aca="false">IF(AND($A93="Yes",TRIM($C93)&lt;&gt;""),"- "&amp;TRIM($C93),"")</f>
         <v/>
       </c>
       <c r="G93" s="0" t="str">
@@ -6626,7 +6626,7 @@
         <v>219</v>
       </c>
       <c r="F94" s="0" t="str">
-        <f aca="false">IF(AND($A94="Yes",$C94&lt;&gt;""),"- "&amp;$C94,"")</f>
+        <f aca="false">IF(AND($A94="Yes",TRIM($C94)&lt;&gt;""),"- "&amp;TRIM($C94),"")</f>
         <v/>
       </c>
       <c r="G94" s="0" t="str">
@@ -6648,7 +6648,7 @@
         <v>222</v>
       </c>
       <c r="F95" s="0" t="str">
-        <f aca="false">IF(AND($A95="Yes",$C95&lt;&gt;""),"- "&amp;$C95,"")</f>
+        <f aca="false">IF(AND($A95="Yes",TRIM($C95)&lt;&gt;""),"- "&amp;TRIM($C95),"")</f>
         <v/>
       </c>
       <c r="G95" s="0" t="str">
@@ -6670,7 +6670,7 @@
         <v>225</v>
       </c>
       <c r="F96" s="0" t="str">
-        <f aca="false">IF(AND($A96="Yes",$C96&lt;&gt;""),"- "&amp;$C96,"")</f>
+        <f aca="false">IF(AND($A96="Yes",TRIM($C96)&lt;&gt;""),"- "&amp;TRIM($C96),"")</f>
         <v/>
       </c>
       <c r="G96" s="0" t="str">
@@ -6692,7 +6692,7 @@
         <v>228</v>
       </c>
       <c r="F97" s="0" t="str">
-        <f aca="false">IF(AND($A97="Yes",$C97&lt;&gt;""),"- "&amp;$C97,"")</f>
+        <f aca="false">IF(AND($A97="Yes",TRIM($C97)&lt;&gt;""),"- "&amp;TRIM($C97),"")</f>
         <v/>
       </c>
       <c r="G97" s="0" t="str">
@@ -6714,7 +6714,7 @@
         <v>231</v>
       </c>
       <c r="F98" s="0" t="str">
-        <f aca="false">IF(AND($A98="Yes",$C98&lt;&gt;""),"- "&amp;$C98,"")</f>
+        <f aca="false">IF(AND($A98="Yes",TRIM($C98)&lt;&gt;""),"- "&amp;TRIM($C98),"")</f>
         <v/>
       </c>
       <c r="G98" s="0" t="str">
@@ -6736,7 +6736,7 @@
         <v>234</v>
       </c>
       <c r="F99" s="0" t="str">
-        <f aca="false">IF(AND($A99="Yes",$C99&lt;&gt;""),"- "&amp;$C99,"")</f>
+        <f aca="false">IF(AND($A99="Yes",TRIM($C99)&lt;&gt;""),"- "&amp;TRIM($C99),"")</f>
         <v/>
       </c>
       <c r="G99" s="0" t="str">
